--- a/competitors/BPM Tool Functional Requirements - Diagramatix.xlsx
+++ b/competitors/BPM Tool Functional Requirements - Diagramatix.xlsx
@@ -3759,7 +3759,7 @@
       </c>
       <c r="G9" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Backup/export exposes repository data (objects, roles, attributes, links) and specific structured exports exist (e.g. the Risk-Control Matrix .xlsx).</t>
+          <t xml:space="preserve">The Risk-Control Matrix, Control Register, GRC Register, traceability graph and coverage summary all export to a multi-sheet Excel workbook in the format auditors expect, giving reportable governance output over the repository.</t>
         </is>
       </c>
       <c r="H9" s="39" t="inlineStr">
@@ -3915,7 +3915,7 @@
       </c>
       <c r="G14" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">The model shows roles (lanes) × tasks × associated data objects, and the Risk-Control Matrix demonstrates tabular projection of model data.</t>
+          <t xml:space="preserve">Governance reporting includes a control-coverage summary (risks with no mitigating control), segregation-of-duties findings, and — where mined — per-control operating-effectiveness, all exportable to Excel for audit and compliance review.</t>
         </is>
       </c>
       <c r="H14" s="39" t="inlineStr">
@@ -7714,7 +7714,7 @@
       </c>
       <c r="G13" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Business rules can be recorded as element properties and edited in the Properties panel; the new Risk-Control Matrix provides an aggregated grid for the risk/control subset.</t>
+          <t xml:space="preserve">Risk and control attributes (likelihood, impact, residual score, control type/frequency/owner, framework reference) are held on catalog objects and surfaced against the steps they are attached to, extending the element-attribute model to governance data.</t>
         </is>
       </c>
       <c r="H13" s="39" t="inlineStr">
@@ -8506,7 +8506,7 @@
       </c>
       <c r="G4" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">The Risk &amp; Control feature attaches Risks to process steps, shows them on the model and produces a Risk-Control Matrix.</t>
+          <t xml:space="preserve">Risks are attached to process steps from an org-adopted Risk &amp; Control catalog and shown on the model. The Risk-Control Matrix exports Activity × Risk × Control, a coverage scan flags any risk with no mitigating control, and — where a mined event log exists — control operating-effectiveness is proven from conformance (“bypassed in N of M cases”).</t>
         </is>
       </c>
       <c r="H4" s="39"/>
@@ -8534,7 +8534,7 @@
       </c>
       <c r="G5" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Risk Managers attach and review Risks on process steps via the Risk &amp; Control feature.</t>
+          <t xml:space="preserve">Controls are attached to the steps they govern from the shared catalog, carry type/frequency/owner/framework attributes, and appear on the model. Control-to-risk mitigation is a first-class link, exported in the Risk-Control Matrix and checked by the coverage and segregation-of-duties rules.</t>
         </is>
       </c>
       <c r="H5" s="39"/>
@@ -8562,7 +8562,7 @@
       </c>
       <c r="G6" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Controls carry framework references (e.g. SOX, ISO 27001) and are attached to steps, so regulatory/control activities are marked on the model.</t>
+          <t xml:space="preserve">Regulations and Policies are first-class GRC objects in the catalog, linked to the Risks and Controls that satisfy them via a directed traceability graph (Risk–Control–Policy–Regulation–Audit Finding–KRI–KPI). Controls also carry framework references (e.g. SOX, ISO 27001). Traceability exports to the GRC register.</t>
         </is>
       </c>
       <c r="H6" s="39"/>
@@ -8590,7 +8590,7 @@
       </c>
       <c r="G7" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Control activities are attached to steps via the Risk &amp; Control feature and appear on the model.</t>
+          <t xml:space="preserve">Audit Findings, KRIs and KPIs are catalog objects linked to the Risks, Controls and steps they relate to, giving end-to-end traceability from regulation down to the process activity and its measured performance. The whole graph exports to Excel for auditors.</t>
         </is>
       </c>
       <c r="H7" s="39"/>
@@ -9019,7 +9019,7 @@
       </c>
       <c r="G5" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">KPIs are recorded as attributes on ArchiMate system/application elements or diagram properties.</t>
+          <t xml:space="preserve">KPIs are first-class GRC catalog objects that can be linked to Risks, Controls and process steps, so process performance targets are traceable alongside the risk and control that govern them; they export in the GRC register.</t>
         </is>
       </c>
       <c r="H5" s="39" t="inlineStr">
@@ -9051,7 +9051,7 @@
       </c>
       <c r="G6" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Suggested measures/KPIs attach to model elements as properties, and the Simulator consumes cycle-time/cost measures.</t>
+          <t xml:space="preserve">KRIs (Key Risk Indicators) are first-class catalog objects linked to the Risks they signal and the Controls that mitigate them, so risk indicators are modelled and traceable, not just documented; they export in the GRC register.</t>
         </is>
       </c>
       <c r="H6" s="39"/>
@@ -10066,7 +10066,7 @@
       </c>
       <c r="G29" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Roles are modelled as lanes, responsibility attributes can be added as task properties, and control owners are captured in the Risk &amp; Control feature.</t>
+          <t xml:space="preserve">Where a process has a mined event log, each control’s operating effectiveness is computed from conformance deviations (“bypassed in N of M cases”) and shown against the control — evidence of control performance over the process lifecycle drawn from real execution data.</t>
         </is>
       </c>
       <c r="H29" s="39" t="inlineStr">

--- a/competitors/BPM Tool Functional Requirements - Diagramatix.xlsx
+++ b/competitors/BPM Tool Functional Requirements - Diagramatix.xlsx
@@ -2435,7 +2435,7 @@
       </c>
       <c r="G6" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Org-master Templates and Entity Lists are admin-controlled, governing what is published for reuse (projects adopt a copy).</t>
+          <t xml:space="preserve">Org-master Templates and Entity Lists are admin-controlled, governing what is published for reuse (projects adopt a copy). Reference and org-tailored APQC PCF frameworks are likewise governed, versioned catalogs adopted per organisation.</t>
         </is>
       </c>
       <c r="H6" s="39"/>
@@ -3759,7 +3759,7 @@
       </c>
       <c r="G9" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">The Risk-Control Matrix, Control Register, GRC Register, traceability graph and coverage summary all export to a multi-sheet Excel workbook in the format auditors expect, giving reportable governance output over the repository.</t>
+          <t xml:space="preserve">The Risk-Control Matrix, Control Register, GRC Register, traceability graph and coverage summary all export to a multi-sheet Excel workbook in the format auditors expect. APQC coverage analytics additionally report which standard processes are modelled versus gaps, by category and level.</t>
         </is>
       </c>
       <c r="H9" s="39" t="inlineStr">
@@ -3915,7 +3915,7 @@
       </c>
       <c r="G14" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Governance reporting includes a control-coverage summary (risks with no mitigating control), segregation-of-duties findings, and — where mined — per-control operating-effectiveness, all exportable to Excel for audit and compliance review.</t>
+          <t xml:space="preserve">Governance reporting includes a control-coverage summary, segregation-of-duties findings, per-control operating-effectiveness where mined, and a roll-up of control-effectiveness by APQC process category — all exportable to Excel for audit and compliance review.</t>
         </is>
       </c>
       <c r="H14" s="39" t="inlineStr">
@@ -4157,7 +4157,7 @@
       </c>
       <c r="G5" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Processes are searchable/filterable by owner, author (modeller) and project; Business Unit/Group is represented via Entity Lists.</t>
+          <t xml:space="preserve">Processes are searchable/filterable by owner, author (modeller) and project; Business Unit/Group is represented via Entity Lists, and APQC PCF classification adds an industry-standard process-category facet.</t>
         </is>
       </c>
       <c r="H5" s="39" t="inlineStr">
@@ -4217,7 +4217,7 @@
       </c>
       <c r="G7" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Processes are searchable by category (proposed/as-is/to-be/target) via diagram type and status.</t>
+          <t xml:space="preserve">Processes are searchable by category (proposed/as-is/to-be/target) via diagram type and status, and by their APQC PCF classification.</t>
         </is>
       </c>
       <c r="H7" s="39"/>
@@ -6651,7 +6651,7 @@
       </c>
       <c r="G3" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">DiagramatixMINER imports process-related event-log data (CSV) from the applications used in a process or set of processes.</t>
+          <t xml:space="preserve">DiagramatixMINER imports process-related event-log data (CSV/TSV, IEEE XES 1849 and OCEL 2.0/1.0) from the applications used in a process or set of processes.</t>
         </is>
       </c>
       <c r="H3" s="39"/>
@@ -8469,17 +8469,17 @@
       </c>
       <c r="F3" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Partially Comply</t>
+          <t xml:space="preserve">Comply</t>
         </is>
       </c>
       <c r="G3" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">ArchiMate modelling and cross-diagram drill-down links relate business processes to capabilities/functions.</t>
+          <t xml:space="preserve">ArchiMate modelling and cross-diagram drill-down relate business processes to capabilities and functions, and the APQC Process Classification Framework (PCF) classifies every process against the industry-standard process taxonomy (Cross-Industry plus industry variants) — a formal, provenance-linked capability/process reference. Coverage analytics then show which standard processes are modelled.</t>
         </is>
       </c>
       <c r="H3" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Capability linkage is via ArchiMate models and links rather than a formal capability-to-process register.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
@@ -8506,7 +8506,7 @@
       </c>
       <c r="G4" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Risks are attached to process steps from an org-adopted Risk &amp; Control catalog and shown on the model. The Risk-Control Matrix exports Activity × Risk × Control, a coverage scan flags any risk with no mitigating control, and — where a mined event log exists — control operating-effectiveness is proven from conformance (“bypassed in N of M cases”).</t>
+          <t xml:space="preserve">Risks are attached to process steps from an org-adopted Risk &amp; Control catalog and shown on the model. The Risk-Control Matrix exports Activity × Risk × Control, a coverage scan flags any risk with no mitigating control, and — where a mined event log exists — control operating-effectiveness is proven from conformance (“bypassed in N of M cases”). Effectiveness is also trended organisation-wide over time in the Compliance Monitoring console and rolled up by APQC process category.</t>
         </is>
       </c>
       <c r="H4" s="39"/>
@@ -8963,7 +8963,7 @@
       </c>
       <c r="G3" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">DiagramatixMINER monitors real value-stream performance from event logs, and the Simulator reports throughput/utilisation/flow-time.</t>
+          <t xml:space="preserve">DiagramatixMINER monitors real value-stream performance from event logs, and the Simulator reports throughput/utilisation/flow-time. The organisation-wide Compliance Monitoring console additionally trends control operating-effectiveness over time across every project — with below-threshold and declining-control alerts — rolled up by APQC process category.</t>
         </is>
       </c>
       <c r="H3" s="39"/>
@@ -8991,7 +8991,7 @@
       </c>
       <c r="G4" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">The Simulator and DiagramatixMINER both report how a process is performing (simulated and actual).</t>
+          <t xml:space="preserve">The Simulator and DiagramatixMINER both report how a process is performing (simulated and actual), and the org-wide Compliance Monitoring console adds continuous, over-time monitoring of control-effectiveness across all projects.</t>
         </is>
       </c>
       <c r="H4" s="39"/>
@@ -9821,17 +9821,17 @@
       </c>
       <c r="F21" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Partially Comply</t>
+          <t xml:space="preserve">Comply</t>
         </is>
       </c>
       <c r="G21" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Projects/folders plus linked Value Chain diagrams and drill-down organise a value-stream process architecture.</t>
+          <t xml:space="preserve">Projects/folders and linked Value Chain diagrams organise a value-stream process architecture, and the APQC Process Classification Framework provides an industry-standard process taxonomy. “Create APQC Project” seeds a project’s entire folder architecture directly from a chosen PCF branch (Category → Process Group → Process → Activity) to any depth.</t>
         </is>
       </c>
       <c r="H21" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Organised via projects/folders and linked value-chain diagrams rather than a dedicated value-stream taxonomy object.</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
@@ -9858,7 +9858,7 @@
       </c>
       <c r="G22" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Multiple linked diagrams and diagram types provide functional, journey and value-stream views of the architecture.</t>
+          <t xml:space="preserve">Multiple linked diagrams and diagram types provide functional, journey and value-stream views of the architecture. Processes can also be classified against the APQC PCF, giving a standard-aligned categorisation with a coverage map of what is modelled versus the framework.</t>
         </is>
       </c>
       <c r="H22" s="39" t="inlineStr">
@@ -9954,7 +9954,7 @@
       </c>
       <c r="G25" s="39" t="inlineStr">
         <is>
-          <t xml:space="preserve">AI Generate (text-to-diagram) and Voice Dictation create process outline diagrams instantly — a true rapid/quick modelling capability.</t>
+          <t xml:space="preserve">AI Generate (text-to-diagram) and Voice Dictation create process outline diagrams instantly — a true rapid/quick modelling capability. “Create APQC Process” also generates a running BPMN model from a chosen standard APQC process in one click (higher-level processes decompose into collapsed sub-processes; task-level processes are AI-generated), so modellers can start straight from the recognised industry standard.</t>
         </is>
       </c>
       <c r="H25" s="39"/>
